--- a/data/trans_bre/P74B-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P74B-Habitat-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>69,64; 82,16</t>
+          <t>69,31; 82,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>36,49; 52,94</t>
+          <t>35,75; 52,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48,14; 63,57</t>
+          <t>47,71; 62,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>575,83; 1260,53</t>
+          <t>592,02; 1312,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>188,13; 418,75</t>
+          <t>178,68; 419,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>319,49; 758,85</t>
+          <t>332,11; 709,15</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>71,16; 83,65</t>
+          <t>71,02; 83,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>45,85; 59,58</t>
+          <t>45,49; 60,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44,5; 58,1</t>
+          <t>43,94; 57,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>644,59; 1403,8</t>
+          <t>658,3; 1371,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>298,02; 633,93</t>
+          <t>289,8; 614,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>268,89; 546,31</t>
+          <t>273,59; 563,47</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>66,22; 81,23</t>
+          <t>65,78; 81,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>49,94; 65,95</t>
+          <t>49,1; 65,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>47,39; 61,68</t>
+          <t>47,61; 62,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>923,11; 2821,01</t>
+          <t>889,33; 2641,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>344,51; 843,02</t>
+          <t>333,7; 846,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>425,12; 1066,63</t>
+          <t>431,45; 1106,39</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>65,9; 79,46</t>
+          <t>66,2; 78,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>58,7; 71,86</t>
+          <t>57,79; 71,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46,49; 61,4</t>
+          <t>46,67; 61,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>622,37; 1380,51</t>
+          <t>625,2; 1388,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>401,05; 881,98</t>
+          <t>386,59; 816,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>235,89; 456,79</t>
+          <t>234,93; 455,51</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>71,91; 78,22</t>
+          <t>71,58; 78,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>51,29; 58,99</t>
+          <t>51,8; 59,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49,88; 57,51</t>
+          <t>49,85; 57,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>810,39; 1228,21</t>
+          <t>803,46; 1228,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>366,32; 545,53</t>
+          <t>363,35; 533,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>363,85; 527,04</t>
+          <t>358,18; 518,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P74B-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P74B-Habitat-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>69,31; 82,38</t>
+          <t>68,94; 81,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>35,75; 52,26</t>
+          <t>34,83; 52,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47,71; 62,59</t>
+          <t>46,76; 62,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>592,02; 1312,57</t>
+          <t>586,71; 1298,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>178,68; 419,97</t>
+          <t>174,16; 416,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>332,11; 709,15</t>
+          <t>320,35; 717,36</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>71,02; 83,59</t>
+          <t>70,52; 83,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>45,49; 60,04</t>
+          <t>45,61; 59,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43,94; 57,7</t>
+          <t>44,03; 58,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>658,3; 1371,27</t>
+          <t>666,99; 1386,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>289,8; 614,11</t>
+          <t>291,47; 589,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>273,59; 563,47</t>
+          <t>263,6; 529,25</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>65,78; 81,34</t>
+          <t>66,12; 81,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>49,1; 65,29</t>
+          <t>49,43; 65,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>47,61; 62,34</t>
+          <t>47,3; 62,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>889,33; 2641,68</t>
+          <t>905,05; 2685,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>333,7; 846,9</t>
+          <t>338,22; 907,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>431,45; 1106,39</t>
+          <t>433,31; 1094,5</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>66,2; 78,99</t>
+          <t>65,59; 79,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>57,79; 71,33</t>
+          <t>58,32; 71,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46,67; 61,24</t>
+          <t>46,71; 61,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>625,2; 1388,82</t>
+          <t>605,72; 1365,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>386,59; 816,61</t>
+          <t>389,99; 835,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>234,93; 455,51</t>
+          <t>242,99; 462,26</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>71,58; 78,49</t>
+          <t>71,72; 78,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>51,8; 59,19</t>
+          <t>51,66; 59,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49,85; 57,32</t>
+          <t>50,14; 57,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>803,46; 1228,43</t>
+          <t>802,34; 1210,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>363,35; 533,68</t>
+          <t>357,72; 529,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>358,18; 518,0</t>
+          <t>352,6; 512,46</t>
         </is>
       </c>
     </row>
